--- a/plantillas/98.xlsx
+++ b/plantillas/98.xlsx
@@ -17,7 +17,7 @@
     <definedName name="MARCA_3">Listas!$F$2:$F$2</definedName>
     <definedName name="MARCA_4">Listas!$G$2:$G$25</definedName>
     <definedName name="MARCA_5">Listas!$H$2:$H$46</definedName>
-    <definedName name="MARCA_6">Listas!$I$2:$I$10</definedName>
+    <definedName name="MARCA_6">Listas!$I$2:$I$9</definedName>
     <definedName name="MARCA_7">Listas!$J$2:$J$4</definedName>
     <definedName name="MARCA_8">Listas!$K$2:$K$6</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$42</definedName>
@@ -32,7 +32,7 @@
     <definedName name="MARCA_18">Listas!$U$2:$U$6</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$13</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$15</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$24</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$25</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$41</definedName>
     <definedName name="MARCA_23">Listas!$Z$2:$Z$5</definedName>
     <definedName name="MARCA_24">Listas!$AA$2:$AA$3</definedName>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>SD ADULT AF SM CORDERO/ARROZ 4.5L · 93506430000</t>
+          <t>SD ADULT 7+ ACT LONG FELINO 4LB · 93506550000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
+          <t>SD ADULT AF SM CORDERO/ARROZ 4.5L · 93506430000</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO D POLLO P/GATO 5.5 · 93500000317</t>
+          <t>D CARU CLASS ESTOFADO DE CERDO/PERRO 12O · 93500000295</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
+          <t>SD ADULTO 1-6  6.6lb · 93509800001</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO DE CERDO/PERRO 12O · 93500000295</t>
+          <t>D CARU CLASS ESTOFADO DE PAVO/PERRO 12OZ · 93500000293</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+ 16.5LB · 93514920001</t>
+          <t>SD ADULTO 1-6 BOCADOS PQNOS 4,4 LB · 93509790001</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO DE PAVO/PERRO 12OZ · 93500000293</t>
+          <t>D CARU SNACK SABOR CARNE P/PERRO 4OZ · 93500000303</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
+          <t>SD ADULTO 7+ 16.5LB · 93514920001</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>D CARU SNACK SABOR CARNE P/PERRO 4OZ · 93500000303</t>
+          <t>D CARU SNACK SABOR CORDERO P/PERRO 4OZ · 93500000305</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+ BOCADOS PQNOS 15LB · 93514930001</t>
+          <t>SD ADULTO 7+ BOCADOS PQNOS  4.4 LB · 93506470001</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>D CARU SNACK SABOR CORDERO P/PERRO 4OZ · 93500000305</t>
+          <t>DCARU CLASS ESTOF D BACALAO P/GATO 5.5OZ · 93500000322</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>SD ADULTO 7+6.6lb · 93506480001</t>
+          <t>SD ADULTO 7+ BOCADOS PQNOS 15LB · 93514930001</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DCARU CLASS ESTOF D BACALAO P/GATO 5.5OZ · 93500000322</t>
+          <t>DCARU CLASS ESTOFADO DE POLLO P/PERRO 12 · 93500000294</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>SD ADULTO BOCADOS PQNOS 15LB · 93514940000</t>
+          <t>SD ADULTO 7+6.6lb · 93506480001</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -10371,11 +10371,6 @@
           <t>BRW ENCORE GOURMET CONEJOS  4LB · 90413020000</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>DCARU CLASS ESTOFADO DE POLLO P/PERRO 12 · 93500000294</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
@@ -10418,7 +10413,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
+          <t>SD ADULTO BOCADOS PQNOS 15LB · 93514940000</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -10550,7 +10545,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
+          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -10677,7 +10672,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>SD ADULTO RAZA GRANDE 15LB · 93514900000</t>
+          <t>SD ADULTO INDOOR FELINO 3.5LB · 93506540000</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -10799,7 +10794,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
+          <t>SD ADULTO RAZA GRANDE 15LB · 93514900000</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -10911,7 +10906,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
+          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -11018,7 +11013,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
+          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -11115,7 +11110,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
+          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -11212,7 +11207,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
+          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -11304,7 +11299,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
+          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -11396,7 +11391,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
+          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -11488,7 +11483,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
+          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -11575,7 +11570,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>SD GATO ADULTO SENSIBLE 3.5LB · 93516940000</t>
+          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -11662,7 +11657,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
+          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -11749,7 +11744,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
+          <t>SD LATA ADULTO POLLO 13OZ · 93509850000</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11826,7 +11821,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>SD MATURE ADULTO 7+ SMALL N TOY 4.5 · 93515530000</t>
+          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -11894,6 +11889,11 @@
       <c r="L25" t="inlineStr">
         <is>
           <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>SD MATURE ADULTO 7+ SMALL N TOY 4.5 · 93515530000</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -15054,16 +15054,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO D POLLO P/GATO 5.5 · 93500000317</t>
+          <t>D CARU CLASS ESTOFADO DE CERDO/PERRO 12O · 93500000295</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000317</t>
+          <t>93500000295</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15074,16 +15074,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO DE CERDO/PERRO 12O · 93500000295</t>
+          <t>D CARU CLASS ESTOFADO DE PAVO/PERRO 12OZ · 93500000293</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000295</t>
+          <t>93500000293</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -15094,16 +15094,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>D CARU CLASS ESTOFADO DE PAVO/PERRO 12OZ · 93500000293</t>
+          <t>D CARU SNACK SABOR CARNE P/PERRO 4OZ · 93500000303</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93500000293</t>
+          <t>93500000303</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -15114,16 +15114,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D CARU SNACK SABOR CARNE P/PERRO 4OZ · 93500000303</t>
+          <t>D CARU SNACK SABOR CORDERO P/PERRO 4OZ · 93500000305</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93500000303</t>
+          <t>93500000305</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -15134,16 +15134,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D CARU SNACK SABOR CORDERO P/PERRO 4OZ · 93500000305</t>
+          <t>DCARU CLASS ESTOF D BACALAO P/GATO 5.5OZ · 93500000322</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93500000305</t>
+          <t>93500000322</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -15154,16 +15154,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DCARU CLASS ESTOF D BACALAO P/GATO 5.5OZ · 93500000322</t>
+          <t>DCARU CLASS ESTOFADO DE POLLO P/PERRO 12 · 93500000294</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93500000322</t>
+          <t>93500000294</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -15174,32 +15174,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DCARU CLASS ESTOFADO DE POLLO P/PERRO 12 · 93500000294</t>
+          <t>CAT CHOW ADULTO HOGARENO 1.5KG · 93520030000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>93500000294</t>
+          <t>93520030000</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CARU</t>
+          <t>CAT CHOW</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CAT CHOW ADULTO HOGARENO 1.5KG · 93520030000</t>
+          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93520030000</t>
+          <t>90408400000</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -15214,16 +15214,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
+          <t>CAT CHOW DEFENSE PLUS PESCADO 9KG · 90408490000</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>90408400000</t>
+          <t>90408490000</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -15234,36 +15234,36 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CAT CHOW DEFENSE PLUS PESCADO 9KG · 90408490000</t>
+          <t>CESAR CACHORRO 100GR · 90028460000</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>90408490000</t>
+          <t>90028460000</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CAT CHOW</t>
+          <t>CESAR</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CESAR CACHORRO 100GR · 90028460000</t>
+          <t>CESAR CARNE 100GR · 90028440000</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>90028460000</t>
+          <t>90028440000</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -15274,16 +15274,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CESAR CARNE 100GR · 90028440000</t>
+          <t>CESAR CORDERO 100GR · 90028480000</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>90028440000</t>
+          <t>90028480000</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -15294,12 +15294,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CESAR CORDERO 100GR · 90028480000</t>
+          <t>CESAR PAVO 100GR · 90028470000</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>90028480000</t>
+          <t>90028470000</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -15314,16 +15314,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CESAR PAVO 100GR · 90028470000</t>
+          <t>CESAR POLLO PARRILLA 100GR · 90028450000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>90028470000</t>
+          <t>90028450000</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -15334,36 +15334,36 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CESAR POLLO PARRILLA 100GR · 90028450000</t>
+          <t>CS ALIM EN LATA P/PERRO MAYOR 13OZ · 93511180000</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>90028450000</t>
+          <t>93511180000</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CESAR</t>
+          <t>CHICKEN SOUP</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CS ALIM EN LATA P/PERRO MAYOR 13OZ · 93511180000</t>
+          <t>CS ALIM LATA  POLLOP/GATITO 5.5OZ · 93511230000</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>93511180000</t>
+          <t>93511230000</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15374,16 +15374,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CS ALIM LATA  POLLOP/GATITO 5.5OZ · 93511230000</t>
+          <t>CS ALIM LATA  POLLOP/GATO AD 5.5OZ · 93511240000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>93511230000</t>
+          <t>93511240000</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15394,16 +15394,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CS ALIM LATA  POLLOP/GATO AD 5.5OZ · 93511240000</t>
+          <t>CS ALIM LATA POLLO/GATO INDOOR 5.5 · 93511260000</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>93511240000</t>
+          <t>93511260000</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15414,16 +15414,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CS ALIM LATA POLLO/GATO INDOOR 5.5 · 93511260000</t>
+          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>93511260000</t>
+          <t>93511250000</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15434,16 +15434,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
+          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>93511250000</t>
+          <t>93511170000</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15454,12 +15454,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
+          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>93511170000</t>
+          <t>93511160000</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -15474,12 +15474,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
+          <t>CS CLASSIC GATO PATE PAVO EN SALSA 5.5OZ · 93500000262</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>93511160000</t>
+          <t>93500000262</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -15494,16 +15494,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE PAVO EN SALSA 5.5OZ · 93500000262</t>
+          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93500000262</t>
+          <t>93500000261</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15514,16 +15514,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
+          <t>CS CLASSIC GATO PATE POLLO Y PESCADO 5.5 · 93500000260</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93500000261</t>
+          <t>93500000260</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15534,16 +15534,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO Y PESCADO 5.5 · 93500000260</t>
+          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93500000260</t>
+          <t>93500000263</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15554,16 +15554,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
+          <t>CS CLASSIC MATURE POLLO RZ PQNA 4.5 · 93518630000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93500000263</t>
+          <t>93518630000</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15574,12 +15574,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CS CLASSIC MATURE POLLO RZ PQNA 4.5 · 93518630000</t>
+          <t>CS CLASSIC POLLO P/ADULTO 13.5LB · 93511080000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93518630000</t>
+          <t>93511080000</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -15594,16 +15594,16 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/ADULTO 13.5LB · 93511080000</t>
+          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93511080000</t>
+          <t>93511070000</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15614,12 +15614,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
+          <t>CS CLASSIC POLLO P/CACHORRO 13.5LB · 93511110000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93511070000</t>
+          <t>93511110000</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -15634,16 +15634,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/CACHORRO 13.5LB · 93511110000</t>
+          <t>CS CLASSIC POLLO P/CACHORRO 4.5LB · 93511100000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>93511110000</t>
+          <t>93511100000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15654,16 +15654,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/CACHORRO 4.5LB · 93511100000</t>
+          <t>CS CLASSIC POLLO P/MATURE 13.5LB · 93511140000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>93511100000</t>
+          <t>93511140000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15674,16 +15674,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/MATURE 13.5LB · 93511140000</t>
+          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>93511140000</t>
+          <t>93511130000</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15694,16 +15694,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
+          <t>CS CLASSIC POLLO/ GATOS ADULT 4.5LB · 93511190000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>93511130000</t>
+          <t>93511190000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15714,16 +15714,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO/ GATOS ADULT 4.5LB · 93511190000</t>
+          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>93511190000</t>
+          <t>93500000252</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15734,16 +15734,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
+          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>93500000252</t>
+          <t>93500000254</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15754,16 +15754,16 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
+          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>93500000254</t>
+          <t>93500000257</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15774,16 +15774,16 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
+          <t>CS GF PERRO LATA POLLO, CARNE, VEGETALES · 93500000256</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>93500000257</t>
+          <t>93500000256</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15794,16 +15794,16 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA POLLO, CARNE, VEGETALES · 93500000256</t>
+          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>93500000256</t>
+          <t>93500000259</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15814,16 +15814,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
+          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>93500000259</t>
+          <t>93500000258</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15834,16 +15834,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
+          <t>CS GRAIN FREE CORDERO/PERRO 10 LB · 93514500000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>93500000258</t>
+          <t>93514500000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15854,16 +15854,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE CORDERO/PERRO 10 LB · 93514500000</t>
+          <t>CS GRAIN FREE CORDERO/PERRO 4 LB · 93514490000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>93514500000</t>
+          <t>93514490000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15874,16 +15874,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE CORDERO/PERRO 4 LB · 93514490000</t>
+          <t>CS GRAIN FREE RES P/PERRO 4 LB · 93514520000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93514490000</t>
+          <t>93514520000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15894,16 +15894,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE RES P/PERRO 4 LB · 93514520000</t>
+          <t>CS GRAIN FREE RES PERRO 10 LB · 93514530000</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>93514520000</t>
+          <t>93514530000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15914,16 +15914,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE RES PERRO 10 LB · 93514530000</t>
+          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93514530000</t>
+          <t>93514460000</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15934,16 +15934,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
+          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>93514460000</t>
+          <t>93514480000</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15954,16 +15954,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
+          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93514480000</t>
+          <t>93500000248</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15974,16 +15974,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
+          <t>CS PERRO ADULTO CARNE Y ARROZ 4.5LB · 93500000250</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93500000248</t>
+          <t>93500000250</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15994,16 +15994,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CS PERRO ADULTO CARNE Y ARROZ 4.5LB · 93500000250</t>
+          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>93500000250</t>
+          <t>93514390000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16014,16 +16014,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
+          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>93514390000</t>
+          <t>93511270000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16034,16 +16034,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
+          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93511270000</t>
+          <t>93514380000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16054,16 +16054,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
+          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93514380000</t>
+          <t>93514410000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16074,16 +16074,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
+          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>93514410000</t>
+          <t>93514420000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16094,16 +16094,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
+          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>93514420000</t>
+          <t>93514660000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16114,12 +16114,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
+          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>93514660000</t>
+          <t>93514680000</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -16134,16 +16134,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
+          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>93514680000</t>
+          <t>93514650000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16154,56 +16154,56 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
+          <t>D CUNIPIC FINCHES 1KG · 93517130000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>93514650000</t>
+          <t>93517130000</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CHICKEN SOUP</t>
+          <t>CUNIPIC</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>D CUNIPIC FINCHES 1KG · 93517130000</t>
+          <t>DOG CHOW ADULT RZ PEQUENA 2KG · 90410400000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>93517130000</t>
+          <t>90410400000</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULT RZ PEQUENA 2KG · 90410400000</t>
+          <t>DOG CHOW ADULT RZ PEQUENA 4KG · 90410390000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90410400000</t>
+          <t>90410390000</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16214,16 +16214,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULT RZ PEQUENA 4KG · 90410390000</t>
+          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>90410390000</t>
+          <t>93512370000</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16234,16 +16234,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
+          <t>DOG CHOW ADULTO 4KG · 93512380000</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>93512370000</t>
+          <t>93512380000</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16254,16 +16254,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 4KG · 93512380000</t>
+          <t>DOG CHOW ADULTO ALTO EN PROTEINA 3.75KG · 90038350000</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>93512380000</t>
+          <t>90038350000</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16274,16 +16274,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO ALTO EN PROTEINA 3.75KG · 90038350000</t>
+          <t>DOG CHOW ADULTO CORDERO 3.75KG MX · 90038370000</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>90038350000</t>
+          <t>90038370000</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16294,16 +16294,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO CORDERO 3.75KG MX · 90038370000</t>
+          <t>DOG CHOW ADULTO MULTI PROTEINAS 3.75KG M · 90038360000</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>90038370000</t>
+          <t>90038360000</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16314,16 +16314,16 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO MULTI PROTEINAS 3.75KG M · 90038360000</t>
+          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>90038360000</t>
+          <t>93512550000</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16334,16 +16334,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA PEQUENA 2KG · 93512550000</t>
+          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>93512550000</t>
+          <t>90038330000</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16354,16 +16354,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS POLLO POUCH 100G MX · 90038330000</t>
+          <t>DOG CHOW CACHORROS RAZAS PEQUENAS 4KG MX · 90038340000</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>90038330000</t>
+          <t>90038340000</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16374,16 +16374,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORROS RAZAS PEQUENAS 4KG MX · 90038340000</t>
+          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>90038340000</t>
+          <t>90038300000</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16394,16 +16394,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DOG CHOW CARNE POUCH 100G MX · 90038300000</t>
+          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>90038300000</t>
+          <t>90038290000</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16414,16 +16414,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DOG CHOW CORDERO POUCH 100G MX · 90038290000</t>
+          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>90038290000</t>
+          <t>90038270000</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16434,16 +16434,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO POUCH 100G MX · 90038270000</t>
+          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>90038270000</t>
+          <t>90038280000</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16454,16 +16454,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DOG CHOW POLLO Y CARNE POUCH 100G MX · 90038280000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>90038280000</t>
+          <t>90038320000</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16474,16 +16474,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DOG CHOW RAZAS PEQUENAS CARNE POUCH 100G · 90038320000</t>
+          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>90038320000</t>
+          <t>90038310000</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16494,36 +16494,36 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DOG CHOW RAZAS PEQUENAS CORDERO POUCH 10 · 90038310000</t>
+          <t>EP SNACK DENTAL CATNIP P/GATO 3OZ · 93509260000</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>90038310000</t>
+          <t>93509260000</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>EMERALD</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL CATNIP P/GATO 3OZ · 93509260000</t>
+          <t>EP SNACK DENTAL POLLO P/GATO 3OZ · 93509210000</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>93509260000</t>
+          <t>93509210000</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16534,16 +16534,16 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL POLLO P/GATO 3OZ · 93509210000</t>
+          <t>EP SNACK DENTAL SABOR ATUN P/GATO 3 · 93509230000</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>93509210000</t>
+          <t>93509230000</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16554,16 +16554,16 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SABOR ATUN P/GATO 3 · 93509230000</t>
+          <t>EP SNACK DENTAL SABOR PESCADO P/GAT · 93509240000</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>93509230000</t>
+          <t>93509240000</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16574,16 +16574,16 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SABOR PESCADO P/GAT · 93509240000</t>
+          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>93509240000</t>
+          <t>93509220000</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -16594,16 +16594,16 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>EP SNACK DENTAL SALMON P/GATO 3OZ · 93509220000</t>
+          <t>EP SNACK P/GATO WHOLLY FISH SALMON · 93514760000</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>93509220000</t>
+          <t>93514760000</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -16614,12 +16614,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EP SNACK P/GATO WHOLLY FISH SALMON · 93514760000</t>
+          <t>EP SNACK P/GATO WHOLLY FISH TUNA 3 · 93514780000</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>93514760000</t>
+          <t>93514780000</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -16634,16 +16634,16 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>EP SNACK P/GATO WHOLLY FISH TUNA 3 · 93514780000</t>
+          <t>EP SNACK PUMPKIN HARVEST ARÁNDANOS 6OZ · 93500000506</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>93514780000</t>
+          <t>93500000506</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16654,16 +16654,16 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EP SNACK PUMPKIN HARVEST ARÁNDANOS 6OZ · 93500000506</t>
+          <t>EP SNACK PUMPKIN HARVEST MANZANA 6OZ · 93500000505</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>93500000506</t>
+          <t>93500000505</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16674,36 +16674,36 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>EP SNACK PUMPKIN HARVEST MANZANA 6OZ · 93500000505</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>93500000505</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>EMERALD</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90312680000</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -16714,12 +16714,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>90312680000</t>
+          <t>90401410000</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -16734,16 +16734,16 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
+          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>90401410000</t>
+          <t>93519340000</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -16754,16 +16754,16 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
+          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>93519340000</t>
+          <t>90330330000</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -16774,16 +16774,16 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>90330330000</t>
+          <t>90330310000</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -16794,16 +16794,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>90330310000</t>
+          <t>90330290000</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -16814,16 +16814,16 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/PERRO · 90330290000</t>
+          <t>PET LAC LECHE EN POLVO P/GATOS 10.5 · 93519350000</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>90330290000</t>
+          <t>93519350000</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -16834,16 +16834,16 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PET LAC LECHE EN POLVO P/GATOS 10.5 · 93519350000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>93519350000</t>
+          <t>93519360000</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -16854,16 +16854,16 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>93519360000</t>
+          <t>90308700000</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -16874,36 +16874,36 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+          <t>EUK DOG LARGE ADULT  15 kg (33.06 lbs) · 90018610000</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>90308700000</t>
+          <t>90018610000</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EUKANUBA</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE ADULT  15 kg (33.06 lbs) · 90018610000</t>
+          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>90018610000</t>
+          <t>90018570000</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -16914,16 +16914,16 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM ADULT  3 Kg (6.61 lbs) · 90018570000</t>
+          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>90018570000</t>
+          <t>90018490000</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -16934,16 +16934,16 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM PUPPY  3 Kg (6.61 lbs) · 90018490000</t>
+          <t>EUK DOG MEDIUM PUPPY 1 Kg (2.20 lbs) · 90018480000</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>90018490000</t>
+          <t>90018480000</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16954,16 +16954,16 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM PUPPY 1 Kg (2.20 lbs) · 90018480000</t>
+          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>90018480000</t>
+          <t>90018630000</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16974,16 +16974,16 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>EUK DOG MEDIUM SENIOR  3 Kg (6.61 lbs) · 90018630000</t>
+          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>90018630000</t>
+          <t>90018560000</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16994,16 +16994,16 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL ADULT  7.5 Kg (16.53 lbs) · 90018560000</t>
+          <t>EUK RZ PEQUENA CONTROL DE PESO 4LB · 93518600000</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>90018560000</t>
+          <t>93518600000</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -17014,36 +17014,36 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>EUK RZ PEQUENA CONTROL DE PESO 4LB · 93518600000</t>
+          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>93518600000</t>
+          <t>90038490000</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>FANCY FEAST</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FANCY FEAST CAZUELA ATUN Y SALMON POUCH · 90038490000</t>
+          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>90038490000</t>
+          <t>93509350000</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -17054,16 +17054,16 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FANCY FEAST CHUNCKY POLLO 3 OZ · 93509350000</t>
+          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>93509350000</t>
+          <t>90038480000</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -17074,16 +17074,16 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FANCY FEAST FILETES PEQ SALMON POUCH · 90038480000</t>
+          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>90038480000</t>
+          <t>90038500000</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -17094,16 +17094,16 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FANCY FEAST PESCADO BLANCO Y TUNA 3OZ US · 90038500000</t>
+          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>90038500000</t>
+          <t>93509370000</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -17114,36 +17114,36 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FANCY FEAST TRUCHA 3 OZ · 93509370000</t>
+          <t>FELIX CARNE 85G MX · 90038460000</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>93509370000</t>
+          <t>90038460000</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>FANCY FEAST</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>FELIX CARNE 85G MX · 90038460000</t>
+          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>90038460000</t>
+          <t>90038450000</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17154,16 +17154,16 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FELIX CARNE GATITOS 85G MX · 90038450000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>90038450000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -17174,16 +17174,16 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038540000</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -17194,16 +17194,16 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DEL MAR ADULTO 1KG MX · 90038540000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>90038540000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -17214,16 +17214,16 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -17234,16 +17234,16 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>93502660000</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -17254,16 +17254,16 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>93502660000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -17274,16 +17274,16 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX POLLO 85G MX · 90038440000</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>90038440000</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17294,32 +17294,32 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FELIX POLLO 85G MX · 90038440000</t>
+          <t>FRUIT MINI SNACK CALABAZA MANGO 5OZ · 90022670000</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>90038440000</t>
+          <t>90022670000</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>FRUITABLES</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FRUIT MINI SNACK CALABAZA MANGO 5OZ · 90022670000</t>
+          <t>FRUIT MINI SNACK MANZANA TOCINO 5OZ · 90022650000</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>90022670000</t>
+          <t>90022650000</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -17334,12 +17334,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>FRUIT MINI SNACK MANZANA TOCINO 5OZ · 90022650000</t>
+          <t>FRUIT MINI SNACK POLLO 5OZ · 90022690000</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>90022650000</t>
+          <t>90022690000</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -17354,12 +17354,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>FRUIT MINI SNACK POLLO 5OZ · 90022690000</t>
+          <t>FRUIT SNACK ATUN CALABAZA P GATOS · 90022620000</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>90022690000</t>
+          <t>90022620000</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -17374,12 +17374,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>FRUIT SNACK ATUN CALABAZA P GATOS · 90022620000</t>
+          <t>FRUIT SNACK CRUNCH BANANA 7OZ · 90022750000</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>90022620000</t>
+          <t>90022750000</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -17394,12 +17394,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH BANANA 7OZ · 90022750000</t>
+          <t>FRUIT SNACK CRUNCH CALABAZA BANANA 12OZ · 90022810000</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>90022750000</t>
+          <t>90022810000</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -17414,12 +17414,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH CALABAZA BANANA 12OZ · 90022810000</t>
+          <t>FRUIT SNACK CRUNCH CALABAZA MANZAN 12OZ · 90022820000</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>90022810000</t>
+          <t>90022820000</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -17434,12 +17434,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH CALABAZA MANZAN 12OZ · 90022820000</t>
+          <t>FRUIT SNACK CRUNCH CALABAZA MORA 12OZ · 90022790000</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>90022820000</t>
+          <t>90022790000</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -17454,12 +17454,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH CALABAZA MORA 12OZ · 90022790000</t>
+          <t>FRUIT SNACK CRUNCH MANZANA 7OZ · 90022740000</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>90022790000</t>
+          <t>90022740000</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -17474,16 +17474,16 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH MANZANA 7OZ · 90022740000</t>
+          <t>FRUIT SNACK CRUNCH MANZANA TOCINO 12OZ · 90022780000</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>90022740000</t>
+          <t>90022780000</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17494,16 +17494,16 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH MANZANA TOCINO 12OZ · 90022780000</t>
+          <t>FRUIT SNACK CRUNCH MORA AZUL 7OZ · 90022730000</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>90022780000</t>
+          <t>90022730000</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17514,12 +17514,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FRUIT SNACK CRUNCH MORA AZUL 7OZ · 90022730000</t>
+          <t>FRUIT SNACK POLLO ARANDANOS P GATOS · 90022590000</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>90022730000</t>
+          <t>90022590000</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -17534,12 +17534,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FRUIT SNACK POLLO ARANDANOS P GATOS · 90022590000</t>
+          <t>FRUIT SNACK SALMON ARANDANOS P GATOS · 90022610000</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>90022590000</t>
+          <t>90022610000</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -17554,36 +17554,36 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>FRUIT SNACK SALMON ARANDANOS P GATOS · 90022610000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>90022610000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>FRUITABLES</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17594,16 +17594,16 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17614,16 +17614,16 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17634,16 +17634,16 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17654,36 +17654,36 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93500000134</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GM COUNT NAT CORDERO/ PESCADO P PERROS 4 · 93500000134</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>93500000134</t>
+          <t>93500000143</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17694,16 +17694,16 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBL/ PERRO 12 · 93500000143</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>93500000143</t>
+          <t>93500000142</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17714,12 +17714,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
+          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>93500000142</t>
+          <t>93500000146</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -17734,16 +17734,16 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>GM COUNT NAT PERROS CACHORROS 4LB · 93500000146</t>
+          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>93500000146</t>
+          <t>93500000139</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17754,16 +17754,16 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 12 · 93500000139</t>
+          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 4L · 93500000138</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>93500000139</t>
+          <t>93500000138</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17774,12 +17774,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>GM COUNT NAT SALMON/ PESCADO P PERROS 4L · 93500000138</t>
+          <t>GM GATOS Y GATITOS COUNTRY NATURALS 3 · 93500000169</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>93500000138</t>
+          <t>93500000169</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -17794,12 +17794,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GM GATOS Y GATITOS COUNTRY NATURALS 3 · 93500000169</t>
+          <t>GM GF GATOS COUNTRY NATURALS INDOOR 4LB · 93500000167</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>93500000169</t>
+          <t>93500000167</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -17814,16 +17814,16 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GM GF GATOS COUNTRY NATURALS INDOOR 4LB · 93500000167</t>
+          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>93500000167</t>
+          <t>93500000130</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17834,16 +17834,16 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNT NATURAL MULTI PROT 4LB · 93500000130</t>
+          <t>GM GF PERRO COUNTRY NATURALS PESCADO 4LB · 93500000126</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>93500000130</t>
+          <t>93500000126</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17854,16 +17854,16 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>GM GF PERRO COUNTRY NATURALS PESCADO 4LB · 93500000126</t>
+          <t>GM PERRO COUNT NATURALS MEZCLA D LA GR 4 · 93500000155</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>93500000126</t>
+          <t>93500000155</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17874,12 +17874,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>GM PERRO COUNT NATURALS MEZCLA D LA GR 4 · 93500000155</t>
+          <t>GM PERRO LOW FAT CNTROL PESO Y SENIOR 4 · 93500000149</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>93500000155</t>
+          <t>93500000149</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -17894,36 +17894,36 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GM PERRO LOW FAT CNTROL PESO Y SENIOR 4 · 93500000149</t>
+          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>93500000149</t>
+          <t>93510560000</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>HIGGINS</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HIGGINS ALIM CONURO Y PERIQ 2.5LB · 93510560000</t>
+          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>93510560000</t>
+          <t>93510480000</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17934,16 +17934,16 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK BOCADOS DE MIJO 1OZ · 93510480000</t>
+          <t>HIGGINS SNACK DE FRUTAS REALES 5OZ · 93510500000</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>93510480000</t>
+          <t>93510500000</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17954,16 +17954,16 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK DE FRUTAS REALES 5OZ · 93510500000</t>
+          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>93510500000</t>
+          <t>93510450000</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17974,16 +17974,16 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS VEGETALES 5OZ · 93510450000</t>
+          <t>HIGGINS SNACK FRUTAS VEGETALES SM 3 · 93510460000</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>93510450000</t>
+          <t>93510460000</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17994,16 +17994,16 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HIGGINS SNACK FRUTAS VEGETALES SM 3 · 93510460000</t>
+          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>93510460000</t>
+          <t>93510430000</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18014,12 +18014,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM COBAYOS 3LB · 93510430000</t>
+          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>93510430000</t>
+          <t>93510440000</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -18034,16 +18034,16 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM P CONEJOS 3LB · 93510440000</t>
+          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>93510440000</t>
+          <t>93518320000</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18054,16 +18054,16 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST ALIM/HAMSTERS 2.5 · 93518320000</t>
+          <t>HIGGINS SUNBURST LORO3LB · 90409690000</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>93518320000</t>
+          <t>90409690000</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18074,12 +18074,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HIGGINS SUNBURST LORO3LB · 90409690000</t>
+          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>90409690000</t>
+          <t>90739860000</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -18094,12 +18094,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HIGGINS VITA LORO 3LBS · 90739860000</t>
+          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>90739860000</t>
+          <t>90416550000</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -18114,16 +18114,16 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HIGGINS VITA SEED CACATUA 2.5 · 90416550000</t>
+          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>90416550000</t>
+          <t>90480080000</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18134,16 +18134,16 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>PROTEINA DE HUEVO PARA AVES 5OZ · 90480080000</t>
+          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>90480080000</t>
+          <t>93504530000</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18154,12 +18154,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS MINERAL GRIT 6 OZ · 93504530000</t>
+          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>93504530000</t>
+          <t>93504540000</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -18174,20 +18174,20 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SNACK HIGGINS SOAK N SPROUT 3 OZ. · 93504540000</t>
+          <t>SD ADULT 7+ ACT LONG FELINO 4LB · 93506550000</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>93504540000</t>
+          <t>93506550000</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>HIGGINS</t>
+          <t>HILL'S</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18243,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18414,16 +18414,16 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
+          <t>SD ADULTO RAZAS PEQUEÑAS Y TOY 4.5 · 93515520000</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>93516920000</t>
+          <t>93515520000</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18434,16 +18434,16 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
+          <t>SD ADULTO SENSIBLE MINI 4LB · 93516920000</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>93516910000</t>
+          <t>93516920000</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18454,12 +18454,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
+          <t>SD ADULTO SMALL Y TOY LIGHT 4.5 · 93516910000</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>93509770000</t>
+          <t>93516910000</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -18474,16 +18474,16 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
+          <t>SD CACHORRO BOCADOS PQN 4.5LB · 93509770000</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>93515510000</t>
+          <t>93509770000</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18494,16 +18494,16 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
+          <t>SD CACHORROS RAZAS PQNAS Y TOY 4.5 · 93515510000</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>90300090000</t>
+          <t>93515510000</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18514,16 +18514,16 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
+          <t>SD FELINE ADULTO 4 LB · 90300090000</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>90303640000</t>
+          <t>90300090000</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18534,16 +18534,16 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
+          <t>SD FELINE GATITO 3.5LB · 90303640000</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>93516930000</t>
+          <t>90303640000</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18554,16 +18554,16 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
+          <t>SD GATITO INDOOR 3.5LB · 93516930000</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>93509830000</t>
+          <t>93516930000</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18574,16 +18574,16 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SD GATO ADULTO SENSIBLE 3.5LB · 93516940000</t>
+          <t>SD GATO ADULT CTRL BOLAS/PELO 3.5 · 93509830000</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>93516940000</t>
+          <t>93509830000</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20403,7 +20403,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -21403,7 +21403,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -21763,7 +21763,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         </is>
       </c>
       <c r="C520" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         </is>
       </c>
       <c r="C597" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -25243,7 +25243,7 @@
         </is>
       </c>
       <c r="C603" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         </is>
       </c>
       <c r="C660" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         </is>
       </c>
       <c r="C662" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         </is>
       </c>
       <c r="C694" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         </is>
       </c>
       <c r="C705" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         </is>
       </c>
       <c r="C764" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>
